--- a/outputs/gold/per_paper_coding_coder_A.xlsx
+++ b/outputs/gold/per_paper_coding_coder_A.xlsx
@@ -10,34 +10,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E-code reference" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R-code reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S001" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S002" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S003" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S004" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S005" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S006" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S007" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S008" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S009" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S010" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S011" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S012" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S013" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S014" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S015" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S016" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S017" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S018" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S019" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S020" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S021" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S022" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S023" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S024" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S025" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S026" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S027" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S028" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE — read this first" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S001" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S002" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S003" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S004" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S005" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S006" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S007" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S008" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S009" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S010" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S011" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S012" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S013" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S014" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S015" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S016" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S017" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S018" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S019" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S020" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S021" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S022" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S023" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S024" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S025" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S026" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S027" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S028" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -109,6 +110,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -578,9 +583,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S007 (2010): Integrated Cases Section: A Course Designed to Promote Clinical Reasoning in Year 2 Medical Students</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S006 (2008): Fostering diagnostic knowledge through computer‐supported, case‐based worked examples: effects of erroneous examples and feedback</t>
         </is>
       </c>
     </row>
@@ -692,9 +697,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S008 (2010): To Think Is Good: Querying an Initial Hypothesis Reduces Diagnostic Error in Medical Students</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S007 (2010): Integrated Cases Section: A Course Designed to Promote Clinical Reasoning in Year 2 Medical Students</t>
         </is>
       </c>
     </row>
@@ -806,9 +811,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S009 (2011): A Novel Educational Tool for Teaching Diagnostic Reasoning and Laboratory Data Interpretation to Veterinary (and Medical) Students</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S008 (2010): To Think Is Good: Querying an Initial Hypothesis Reduces Diagnostic Error in Medical Students</t>
         </is>
       </c>
     </row>
@@ -920,9 +925,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S010 (2011): Bringing Explicit Insight into Cognitive Psychology Features during Clinical Reasoning Seminars: A Prospective, Controlled Study</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S009 (2011): A Novel Educational Tool for Teaching Diagnostic Reasoning and Laboratory Data Interpretation to Veterinary (and Medical) Students</t>
         </is>
       </c>
     </row>
@@ -1034,9 +1039,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S011 (2011): How we created virtual patient cases for primary care-based learning</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S010 (2011): Bringing Explicit Insight into Cognitive Psychology Features during Clinical Reasoning Seminars: A Prospective, Controlled Study</t>
         </is>
       </c>
     </row>
@@ -1148,9 +1153,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S012 (2011): The Efficacy of a Targeted Remediation Process for Students Who Fail Standardized Patient Examinations</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S011 (2011): How we created virtual patient cases for primary care-based learning</t>
         </is>
       </c>
     </row>
@@ -1262,9 +1267,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S013 (2011): The influence of medical students selfexplanations on diagnostic performance</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S012 (2011): The Efficacy of a Targeted Remediation Process for Students Who Fail Standardized Patient Examinations</t>
         </is>
       </c>
     </row>
@@ -1376,9 +1381,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S014 (2012): evPaeds: undergraduate clinical reasoning</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S013 (2011): The influence of medical students selfexplanations on diagnostic performance</t>
         </is>
       </c>
     </row>
@@ -1490,9 +1495,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S015 (2012): Preparing medical students for clinical decision making: A pilot study exploring how students make decisions and the perceived impact of a clinical decision making teaching intervention</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S014 (2012): evPaeds: undergraduate clinical reasoning</t>
         </is>
       </c>
     </row>
@@ -1604,9 +1609,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S016 (2012): Reflection as a strategy to foster medical students acquisition of diagnostic competence</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S015 (2012): Preparing medical students for clinical decision making: A pilot study exploring how students make decisions and the perceived impact of a clinical decision making teaching intervention</t>
         </is>
       </c>
     </row>
@@ -2794,9 +2799,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S017 (2012): Should we teach using schemas? Evidence from a randomised trial</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S016 (2012): Reflection as a strategy to foster medical students acquisition of diagnostic competence</t>
         </is>
       </c>
     </row>
@@ -2908,9 +2913,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S018 (2012): What and how advanced medical students learn</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S017 (2012): Should we teach using schemas? Evidence from a randomised trial</t>
         </is>
       </c>
     </row>
@@ -3022,9 +3027,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S019 (2013): Effect of enhanced analytic reasoning on diagnostic accuracy: A randomized controlled study</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S018 (2012): What and how advanced medical students learn</t>
         </is>
       </c>
     </row>
@@ -3136,9 +3141,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S020 (2013): Students selfexplanations while solving unfamiliar cases: the role of biomedical knowledge</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S019 (2013): Effect of enhanced analytic reasoning on diagnostic accuracy: A randomized controlled study</t>
         </is>
       </c>
     </row>
@@ -3250,9 +3255,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S021 (2013): To what extent does nonanalytic reasoning contribute to visual learning in cytopathology?</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S020 (2013): Students selfexplanations while solving unfamiliar cases: the role of biomedical knowledge</t>
         </is>
       </c>
     </row>
@@ -3364,9 +3369,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S022 (2014): A Serious Game Can Be a Valid Method to Train Clinical</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S021 (2013): To what extent does nonanalytic reasoning contribute to visual learning in cytopathology?</t>
         </is>
       </c>
     </row>
@@ -3478,9 +3483,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S023 (2014): Casebook: a virtual patient iPad application for teaching decision-making through the use of electronic health records</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S022 (2014): A Serious Game Can Be a Valid Method to Train Clinical</t>
         </is>
       </c>
     </row>
@@ -3592,9 +3597,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S024 (2014): Ineffectiveness of cognitive forcing strategies</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S023 (2014): Casebook: a virtual patient iPad application for teaching decision-making through the use of electronic health records</t>
         </is>
       </c>
     </row>
@@ -3706,9 +3711,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S025 (2015): Does medical students’ diagnostic performance improve by observing examples of self-explanation provided by peers or experts?</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S024 (2014): Ineffectiveness of cognitive forcing strategies</t>
         </is>
       </c>
     </row>
@@ -3820,9 +3825,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S026 (2015): Self&amp;#x2010;explanation in learning clinical reasoning: the added value of examples and prompts</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S025 (2015): Does medical students’ diagnostic performance improve by observing examples of self-explanation provided by peers or experts?</t>
         </is>
       </c>
     </row>
@@ -4856,9 +4861,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S027 (2016): Test&amp;#x2010;enhanced learning of clinical reasoning: a crossover randomised trial</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S026 (2015): Self&amp;#x2010;explanation in learning clinical reasoning: the added value of examples and prompts</t>
         </is>
       </c>
     </row>
@@ -4970,9 +4975,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S028 (None): 18  Reprinted from Australian Family Physician Vol. 41, No. 1/2 january/february 2012</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S027 (2016): Test&amp;#x2010;enhanced learning of clinical reasoning: a crossover randomised trial</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5084,9 +5089,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S001 (2001): Coordination of Analytic and Similarity-Based Processing Strategies and Expertise in Dermatological Diagnosis</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S028 (None): 18  Reprinted from Australian Family Physician Vol. 41, No. 1/2 january/february 2012</t>
         </is>
       </c>
     </row>
@@ -5179,6 +5184,286 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE. This is what ONE coded paper looks like. Do not edit this sheet — it is here to show you the target. Each study sheet has these same seven columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The source sentence is Richmond et al. (2020) p.714, where the authors marked the elements themselves:  "When an expert's reasoning processes or thoughts are explicitly revealed and discussed (Mresource) with students with sufficient domain-specific knowledge (C), this promotes understanding (Mresponse) leading to insight (Mresponse) into the reasoning process (O) and a positive learning experience (O)."   That one sentence becomes the four rows below: one CMOC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CMOC #</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Element type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>E-code</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Your label</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verbatim quote</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Polarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>students with high domain-specific knowledge</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>students with sufficient domain-specific knowledge</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mechanism_Resource</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>expert's reasoning made explicit and discussed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>an expert's reasoning processes or thoughts are explicitly revealed and discussed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mechanism_Response</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>understanding of the reasoning process</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>this promotes understanding</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>positive learning experience</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>a positive learning experience</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT:</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * All four rows share CMOC # = 1, because they are one causal story. The next story in the same paper would be CMOC # 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 'Your label' is your own short wording. 'Verbatim quote' must be copied from the paper exactly — if you cannot find a sentence, do not code that element.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * E-code is the closest match from the 'E-code reference' sheet, or type NEW if the paper says something genuinely outside that list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Most papers give 2-5 CMOCs. Twenty means you are coding sentences, not claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>THE DISTINCTION PEOPLE GET WRONG MOST OFTEN:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mechanism_Response = inside one learner's head (understood, panicked, felt at ease).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Outcome            = a result you could put in a results table (accuracy rose, scores unchanged, similar decision speed across groups).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  'The two groups showed similar decision speed' is an OUTCOME, not a response — even though it is about learners.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5198,9 +5483,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S002 (2003): “Clinical Reasoning Theater”</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S001 (2001): Coordination of Analytic and Similarity-Based Processing Strategies and Expertise in Dermatological Diagnosis</t>
         </is>
       </c>
     </row>
@@ -5312,9 +5597,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S003 (2006): Giving Learners the Best of Both Worlds: Do Clinical Teachers Need to Guard Against Teaching Pattern Recognition to Novices?</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S002 (2003): “Clinical Reasoning Theater”</t>
         </is>
       </c>
     </row>
@@ -5426,9 +5711,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S004 (2007): Teaching from the clinical reasoning literature: combined reasoning strategies help novice diagnosticians overcome misleading information</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S003 (2006): Giving Learners the Best of Both Worlds: Do Clinical Teachers Need to Guard Against Teaching Pattern Recognition to Novices?</t>
         </is>
       </c>
     </row>
@@ -5540,9 +5825,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S005 (2007): The benefits of flexibility: the pedagogical value of instructions to adopt multifaceted diagnostic reasoning strategies</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S004 (2007): Teaching from the clinical reasoning literature: combined reasoning strategies help novice diagnosticians overcome misleading information</t>
         </is>
       </c>
     </row>
@@ -5654,9 +5939,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>S006 (2008): Fostering diagnostic knowledge through computer‐supported, case‐based worked examples: effects of erroneous examples and feedback</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>S005 (2007): The benefits of flexibility: the pedagogical value of instructions to adopt multifaceted diagnostic reasoning strategies</t>
         </is>
       </c>
     </row>
